--- a/docs/acceptance/phase-space-v1/artifacts/phase-space-dashboard.xlsx
+++ b/docs/acceptance/phase-space-v1/artifacts/phase-space-dashboard.xlsx
@@ -34,212 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="68">
-  <si>
-    <t>Website Analytics Dashboard</t>
-  </si>
-  <si>
-    <t>SELECTED REPORTING PERIOD</t>
-  </si>
-  <si>
-    <t>DATA CURRENT THROUGH</t>
-  </si>
-  <si>
-    <t>Dashboard</t>
-  </si>
-  <si>
-    <t>ACTIVE USERS</t>
-  </si>
-  <si>
-    <t>NEW USERS</t>
-  </si>
-  <si>
-    <t>30-DAY RETENTION</t>
-  </si>
-  <si>
-    <t>TRIAL-TO-PAID</t>
-  </si>
-  <si>
-    <t>vs prior</t>
-  </si>
-  <si>
-    <t>vs target</t>
-  </si>
-  <si>
-    <t>SESSIONS / USER</t>
-  </si>
-  <si>
-    <t>MONTHLY RECURRING REVENUE</t>
-  </si>
-  <si>
-    <t>BOUNCE RATE</t>
-  </si>
-  <si>
-    <t>MRR / ACTIVE USER</t>
-  </si>
-  <si>
-    <t>ACTIVE USERS — ACTUAL VS TARGET</t>
-  </si>
-  <si>
-    <t>MRR — ACTUAL VS TARGET</t>
-  </si>
-  <si>
-    <t>CONVERSION FUNNEL — SELECTED PERIOD</t>
-  </si>
-  <si>
-    <t>MRR MIX BY SEGMENT</t>
-  </si>
-  <si>
-    <t>SELECTED-PERIOD VARIANCE</t>
-  </si>
-  <si>
-    <t>Metric</t>
-  </si>
-  <si>
-    <t>Goal</t>
-  </si>
-  <si>
-    <t>Actual</t>
-  </si>
-  <si>
-    <t>Target</t>
-  </si>
-  <si>
-    <t>Absolute Variance</t>
-  </si>
-  <si>
-    <t>Variance %</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Status is direction-aware: most metrics favor higher results, while Bounce Rate explicitly favors lower results. Watch thresholds are within 5% of target.</t>
-  </si>
-  <si>
-    <t>Synthetic illustrative data for template use.</t>
-  </si>
-  <si>
-    <t>Data &amp; Targets</t>
-  </si>
-  <si>
-    <t>HOW TO USE</t>
-  </si>
-  <si>
-    <t>Paste or replace synthetic monthly actuals and targets in yellow cells B15:P26. Keep dates as real month-start dates.</t>
-  </si>
-  <si>
-    <t>Choose Selected Period in C8. Dashboard KPIs, comparisons, variance status, funnel, and mix recalculate from that period.</t>
-  </si>
-  <si>
-    <t>Selected Period</t>
-  </si>
-  <si>
-    <t>Data Current Through</t>
-  </si>
-  <si>
-    <t>Source Note</t>
-  </si>
-  <si>
-    <t>Synthetic generic example data for template review; replace only yellow inputs.</t>
-  </si>
-  <si>
-    <t>MONTHLY ACTUALS &amp; TARGETS — EDIT YELLOW CELLS</t>
-  </si>
-  <si>
-    <t>Period</t>
-  </si>
-  <si>
-    <t>Active Users</t>
-  </si>
-  <si>
-    <t>New Users</t>
-  </si>
-  <si>
-    <t>30-Day Retention</t>
-  </si>
-  <si>
-    <t>Trial-to-Paid Conversion</t>
-  </si>
-  <si>
-    <t>Sessions / User</t>
-  </si>
-  <si>
-    <t>MRR</t>
-  </si>
-  <si>
-    <t>Bounce Rate</t>
-  </si>
-  <si>
-    <t>Active Users Target</t>
-  </si>
-  <si>
-    <t>New Users Target</t>
-  </si>
-  <si>
-    <t>Retention Target</t>
-  </si>
-  <si>
-    <t>Conversion Target</t>
-  </si>
-  <si>
-    <t>Sessions Target</t>
-  </si>
-  <si>
-    <t>MRR Target</t>
-  </si>
-  <si>
-    <t>Bounce Target</t>
-  </si>
-  <si>
-    <t>FUNNEL DRIVERS — EDIT YELLOW CELLS</t>
-  </si>
-  <si>
-    <t>SEGMENT MIX — EDIT YELLOW CELLS</t>
-  </si>
-  <si>
-    <t>Driver</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Segment</t>
-  </si>
-  <si>
-    <t>Share</t>
-  </si>
-  <si>
-    <t>Visitors per active user</t>
-  </si>
-  <si>
-    <t>Enterprise</t>
-  </si>
-  <si>
-    <t>Visitor to signup</t>
-  </si>
-  <si>
-    <t>Midmarket</t>
-  </si>
-  <si>
-    <t>Signup completion</t>
-  </si>
-  <si>
-    <t>SMB</t>
-  </si>
-  <si>
-    <t>Workspace activation</t>
-  </si>
-  <si>
-    <t>Self-Svc</t>
-  </si>
-  <si>
-    <t>Activation to paid</t>
-  </si>
-  <si>
-    <t>Share Check</t>
-  </si>
-</sst>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="0" uniqueCount="0"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1903,6 +1698,7 @@
       <ns0:valAx>
         <ns0:axId val="2009006557"/>
         <ns0:scaling>
+          <ns0:logBase val="10"/>
           <ns0:orientation val="minMax"/>
         </ns0:scaling>
         <ns0:delete val="0"/>
@@ -2578,7 +2374,7 @@
     <row r="4" spans="2:17" ht="20" customHeight="1" ns3:dyDescent="0.15">
       <c r="B4" s="46" t="inlineStr">
         <is>
-          <t>Build 3745369692fd; 36/36 runs. Dirty runs are non-quotable. See Runs and report for provenance.</t>
+          <t>Build 3745369692fd; 36/36 runs. Tiles show the selected case; worst across all runs: frame p95 10.43 ms, age p95 40.97 ms. Dirty runs are non-quotable.</t>
         </is>
       </c>
       <c r="C4" s="46"/>
@@ -4020,7 +3816,7 @@
       </c>
       <c r="C11" s="84" t="inlineStr">
         <is>
-          <t>Build 3745369692fd; 36/36 runs. Dirty runs are non-quotable. See Runs and report for provenance.</t>
+          <t>Build 3745369692fd; 36/36 runs. Tiles show the selected case; worst across all runs: frame p95 10.43 ms, age p95 40.97 ms. Dirty runs are non-quotable.</t>
         </is>
       </c>
       <c r="D11" s="84"/>
